--- a/SentraTech_Website_Content_Change_Tracker.xlsx
+++ b/SentraTech_Website_Content_Change_Tracker.xlsx
@@ -10,9 +10,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEO Tracker" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Realtime Audit" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Site Issues" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEO Growth Plan (90-Day)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Realtime Audit" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Site Issues" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'SEO Tracker'!$A$1:$N$79</definedName>
@@ -26,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -128,8 +129,37 @@
       <color rgb="00B45309"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF1f4e78"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF1f4e78"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="FFb71c1c"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -186,8 +216,23 @@
         <fgColor rgb="FFd9eaf7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFe0f2f1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0e7490"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFfff3cd"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -314,11 +359,69 @@
         <color rgb="00D0D7DE"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -482,6 +585,41 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2107,7 +2245,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.005" bestFit="1" customWidth="1" style="38" min="1" max="1"/>
@@ -2247,7 +2385,7 @@
       <c r="L2" s="55" t="inlineStr"/>
       <c r="M2" s="56" t="inlineStr">
         <is>
-          <t>HTTP 404 on live check</t>
+          <t>Investigated 2026-08-15: file does not exist anywhere in /image/solutions/showcase/bridge inspection/ under any name. Directory only has Condition Assessment Report.webp, Drone-based bridge inspection...webp, NDT Ultrasonic Testing.webp, Underwater Bridge Foundation.webp. Needs the real asset supplied (or the reference repointed) by the site owner — not a code fix.</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3661,7 @@
       </c>
       <c r="G24" s="56" t="inlineStr">
         <is>
-          <t>Meta description trimmed to &lt;= 160 chars</t>
+          <t>A guide to strain gauges: how they work, the main types (foil, wire, semiconductor, vibrating wire), the gauge factor formula, and structural monitoring uses.</t>
         </is>
       </c>
       <c r="H24" s="56" t="inlineStr">
@@ -3536,16 +3674,20 @@
           <t>Realtime Audit (auto)</t>
         </is>
       </c>
-      <c r="J24" s="55" t="inlineStr"/>
+      <c r="J24" s="55" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
       <c r="K24" s="55" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L24" s="55" t="inlineStr"/>
       <c r="M24" s="56" t="inlineStr">
         <is>
-          <t>Meta 184 chars</t>
+          <t>Fixed 2026-08-15: now 158 chars.</t>
         </is>
       </c>
     </row>
@@ -3582,7 +3724,7 @@
       </c>
       <c r="G25" s="56" t="inlineStr">
         <is>
-          <t>Meta description trimmed to &lt;= 160 chars</t>
+          <t>How digital inclinometers and tiltmeters measure tilt and rotation, the difference between the two, and their use in slope and structural monitoring.</t>
         </is>
       </c>
       <c r="H25" s="56" t="inlineStr">
@@ -3595,16 +3737,20 @@
           <t>Realtime Audit (auto)</t>
         </is>
       </c>
-      <c r="J25" s="55" t="inlineStr"/>
+      <c r="J25" s="55" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
       <c r="K25" s="55" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L25" s="55" t="inlineStr"/>
       <c r="M25" s="56" t="inlineStr">
         <is>
-          <t>Meta 170 chars</t>
+          <t>Fixed 2026-08-15: now 149 chars.</t>
         </is>
       </c>
     </row>
@@ -3641,7 +3787,7 @@
       </c>
       <c r="G26" s="56" t="inlineStr">
         <is>
-          <t>Title trimmed to &lt;= 60 chars</t>
+          <t>What Is an Accelerometer Sensor? Types &amp; Applications</t>
         </is>
       </c>
       <c r="H26" s="56" t="inlineStr">
@@ -3654,16 +3800,20 @@
           <t>Realtime Audit (auto)</t>
         </is>
       </c>
-      <c r="J26" s="55" t="inlineStr"/>
+      <c r="J26" s="55" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
       <c r="K26" s="55" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L26" s="55" t="inlineStr"/>
       <c r="M26" s="56" t="inlineStr">
         <is>
-          <t>Title 72 chars</t>
+          <t>Fixed 2026-08-15: now 53 chars.</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3850,7 @@
       </c>
       <c r="G27" s="56" t="inlineStr">
         <is>
-          <t>Meta description trimmed to &lt;= 160 chars</t>
+          <t>How accelerometer sensors work, piezoelectric vs capacitive MEMS types, and how they're used for seismic, structural and machinery monitoring.</t>
         </is>
       </c>
       <c r="H27" s="56" t="inlineStr">
@@ -3713,16 +3863,20 @@
           <t>Realtime Audit (auto)</t>
         </is>
       </c>
-      <c r="J27" s="55" t="inlineStr"/>
+      <c r="J27" s="55" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
       <c r="K27" s="55" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L27" s="55" t="inlineStr"/>
       <c r="M27" s="56" t="inlineStr">
         <is>
-          <t>Meta 177 chars</t>
+          <t>Fixed 2026-08-15: now 142 chars.</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3972,7 @@
       </c>
       <c r="G29" s="56" t="inlineStr">
         <is>
-          <t>Meta description trimmed to &lt;= 160 chars</t>
+          <t>What a data logger is, how it works, the main types (temperature, analog, vibrating wire, wireless IoT), and how to choose one for remote monitoring.</t>
         </is>
       </c>
       <c r="H29" s="56" t="inlineStr">
@@ -3831,16 +3985,20 @@
           <t>Realtime Audit (auto)</t>
         </is>
       </c>
-      <c r="J29" s="55" t="inlineStr"/>
+      <c r="J29" s="55" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
       <c r="K29" s="55" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L29" s="55" t="inlineStr"/>
       <c r="M29" s="56" t="inlineStr">
         <is>
-          <t>Meta 166 chars</t>
+          <t>Fixed 2026-08-15: now 149 chars.</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4566,7 @@
       </c>
       <c r="G39" s="56" t="inlineStr">
         <is>
-          <t>Meta description trimmed to &lt;= 160 chars</t>
+          <t>LCC by XGRIDS — capture, create and share 3D Gaussian Splatting models with Studio, Cloud, Model &amp; Scene Editor, available in India via Sentra.</t>
         </is>
       </c>
       <c r="H39" s="56" t="inlineStr">
@@ -4421,16 +4579,20 @@
           <t>Realtime Audit (auto)</t>
         </is>
       </c>
-      <c r="J39" s="55" t="inlineStr"/>
+      <c r="J39" s="55" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
       <c r="K39" s="55" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L39" s="55" t="inlineStr"/>
       <c r="M39" s="56" t="inlineStr">
         <is>
-          <t>Meta 203 chars</t>
+          <t>Fixed 2026-08-15: now 143 chars.</t>
         </is>
       </c>
     </row>
@@ -4526,7 +4688,7 @@
       </c>
       <c r="G41" s="56" t="inlineStr">
         <is>
-          <t>Meta description trimmed to &lt;= 160 chars</t>
+          <t>LixelStudio by XGRIDS — one-click processing from raw scan data to production-ready point clouds, with SLAM mapping and BIM/CAD/GIS export, via Sentra.</t>
         </is>
       </c>
       <c r="H41" s="56" t="inlineStr">
@@ -4539,16 +4701,20 @@
           <t>Realtime Audit (auto)</t>
         </is>
       </c>
-      <c r="J41" s="55" t="inlineStr"/>
+      <c r="J41" s="55" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
       <c r="K41" s="55" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L41" s="55" t="inlineStr"/>
       <c r="M41" s="56" t="inlineStr">
         <is>
-          <t>Meta 222 chars</t>
+          <t>Fixed 2026-08-15: now 151 chars.</t>
         </is>
       </c>
     </row>
@@ -5315,13 +5481,440 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="18.75" customHeight="1"/>
-    <row r="56" ht="18.75" customHeight="1"/>
-    <row r="57" ht="18.75" customHeight="1"/>
-    <row r="58" ht="18.75" customHeight="1"/>
-    <row r="59" ht="18.75" customHeight="1"/>
-    <row r="60" ht="18.75" customHeight="1"/>
-    <row r="61" ht="18.75" customHeight="1"/>
+    <row r="55" ht="18.75" customHeight="1">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CHG-0054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>/products/laser-scanners.html, /blogs/top-5-hidden-structural-damages-bridge-inspection.html, /blogs/intelligent-pump-house-monitoring-and-control.html</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Links</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Internal href paths</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>href="./products/..." / href="./solutions/..." — resolved one directory too deep (e.g. /products/products/lcc.html, /blogs/solutions/structural-health-monitoring.html), returning 404</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Corrected relative paths (./lcc.html etc. on the products page; ../solutions/..., ../products/... on the two blog pages)</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Fixed 12 internal links returning 404 (Ahrefs: 404 pages / broken-link reports), caused by a relative-path depth bug.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>SEO Audit (Ahrefs)</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>5 links on laser-scanners.html, 4 on top-5-hidden-structural-damages-bridge-inspection.html, 3 on intelligent-pump-house-monitoring-and-control.html.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18.75" customHeight="1">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>CHG-0055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>/js/script.js</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Nav path-prefix logic</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Subfolder-detection list (pathPrefix / fixNavLinks) omitted '/industries/'</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Added '/industries/' to both subfolder-detection lists</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Live bug: all 8 /industries/*.html pages fetched header.html/footer.html/sidebar.html from the wrong relative path (404), shipping with no navigation for real visitors.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Code Review</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Found while investigating the Ahrefs 'canonical URL has no incoming internal links' report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18.75" customHeight="1">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>CHG-0056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>80 pages (all pages with header/footer/sidebar includes), /js/script.js, /scripts/inline-partials.mjs (new), /netlify.toml</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Internal link crawlability</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Header/footer/sidebar only existed after a client-side JS fetch; crawlers saw empty &lt;div id="header"&gt;&lt;/div&gt; placeholders and no &lt;a&gt; links</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Added scripts/inline-partials.mjs, which bakes header.html/footer.html/sidebar.html directly into each page at build time (depth-aware relative paths); script.js now skips the runtime fetch when content is already baked</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Resolves Ahrefs 'Canonical URL has no incoming internal links' (76 pages) and 'Orphan page' (glossary.html, document-center.html) — crawlers now see real &lt;a&gt; markup instead of only-after-JS content.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>SEO Audit (Ahrefs)</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Wired into Netlify build command (npm install &amp;&amp; node scripts/inline-partials.mjs) as a safety net for future pages that ship with the placeholder still empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18.75" customHeight="1">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>CHG-0057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>/blogs/structural-health-monitoring.html</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Broken Image</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Image src</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>src="./image/blogs/blog1_picture.webp" (resolved to /blogs/image/..., 404)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>src="../image/blogs/blog1_picture.webp"</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Fixed broken image (Ahrefs: Page has broken image) — same relative-path depth bug as CHG-0054.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>SEO Audit (Ahrefs)</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>File exists at /image/blogs/blog1_picture.webp; only the reference was wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18.75" customHeight="1">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>CHG-0058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>/netlify.toml</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Redirect config</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>No explicit www/https redirect rule — Netlify auto-generated a 2-hop chain (http://www → https://www → https://sentratech.in)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Added explicit 301 redirects for http(s)://www.sentratech.in/* → https://sentratech.in/:splat</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Collapses the Ahrefs-flagged redirect chain to a single hop.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>SEO Audit (Ahrefs)</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Netlify confirmed as the live deploy target; also added the inline-partials build step to the Netlify build command (see CHG-0056).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18.75" customHeight="1">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>CHG-0059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>/article/revolutionizing-infrastructure-monitoring-with-iot.html</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SEO - Meta Description</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Meta description</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>How wireless sensors, edge gateways and digital twins turn bridges, pump houses and rail assets into self-reporting infrastructure that flags problems before they fail. (168 chars)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>How wireless sensors, edge gateways and digital twins turn bridges, pump houses and rail assets into self-reporting infrastructure that flags problems early. (157 chars)</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Trim meta description to &lt;= 160 chars.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>SEO Audit (Ahrefs)</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Not previously tracked in this sheet (only picked up by the newer Ahrefs crawl).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18.75" customHeight="1">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CHG-0060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>/index.html, /solutions.html</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Accessibility / Alt Text</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>img alt attribute</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>32 images flagged by Ahrefs as missing/empty alt text</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Reviewed — no change made</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>All 32 are duplicate marquee "Set B" cards inside aria-hidden="true" containers (built for a seamless infinite-scroll loop). Empty alt="" on hidden decorative duplicates is correct per WCAG — the same card's real, visible copy elsewhere on the page already has descriptive alt text.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>SEO Audit (Ahrefs)</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>False positive confirmed by inspecting every flagged instance. Adding real alt text here would be an accessibility regression (duplicate screen-reader announcements).</t>
+        </is>
+      </c>
+    </row>
     <row r="62" ht="18.75" customHeight="1"/>
     <row r="63" ht="18.75" customHeight="1"/>
     <row r="64" ht="18.75" customHeight="1"/>
@@ -6135,7 +6728,7 @@
       </c>
       <c r="F6" s="56" t="inlineStr">
         <is>
-          <t>Discover how IoT is transforming infrastructure monitoring with real-time data analytics, enabling proactive maintenance and optimized operations.</t>
+          <t>How wireless sensors, edge gateways and digital twins turn bridges, pump houses and rail assets into self-reporting infrastructure that flags problems early.</t>
         </is>
       </c>
       <c r="G6" s="55" t="n">
@@ -6156,7 +6749,7 @@
       </c>
       <c r="K6" s="56" t="inlineStr">
         <is>
-          <t>Discover how IoT is transforming infrastructure monitoring with real-time data analytics, enabling proactive maintenance and optimized operations.</t>
+          <t>How wireless sensors, edge gateways and digital twins turn bridges, pump houses and rail assets into self-reporting infrastructure that flags problems early.</t>
         </is>
       </c>
       <c r="L6" s="55" t="inlineStr">
@@ -6166,10 +6759,14 @@
       </c>
       <c r="M6" s="55" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="N6" s="56" t="inlineStr"/>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="N6" s="56" t="inlineStr">
+        <is>
+          <t>Meta description fixed 2026-08-15 (157 chars)</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="55" t="inlineStr">
@@ -7063,7 +7660,7 @@
       </c>
       <c r="F21" s="56" t="inlineStr">
         <is>
-          <t>What a data logger is, how it works, the main types (temperature, analog, vibrating wire, wireless IoT), and what to look for when choosing one for remote monitoring.</t>
+          <t>What a data logger is, how it works, the main types (temperature, analog, vibrating wire, wireless IoT), and how to choose one for remote monitoring.</t>
         </is>
       </c>
       <c r="G21" s="55" t="n">
@@ -7084,7 +7681,7 @@
       </c>
       <c r="K21" s="56" t="inlineStr">
         <is>
-          <t>What a data logger is, how it works, the main types (temperature, analog, vibrating wire, wireless IoT), and what to look for when choosing one for remote monitoring.</t>
+          <t>What a data logger is, how it works, the main types (temperature, analog, vibrating wire, wireless IoT), and how to choose one for remote monitoring.</t>
         </is>
       </c>
       <c r="L21" s="55" t="inlineStr">
@@ -7094,12 +7691,12 @@
       </c>
       <c r="M21" s="55" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N21" s="56" t="inlineStr">
         <is>
-          <t>Title 63 chars (&gt;60); Meta 166 chars (&gt;160)</t>
+          <t>Title 63 chars (&gt;60) - not addressed (Ahrefs SEO audit only flagged titles &gt;70 chars); Meta description fixed 2026-08-15 (149 chars)</t>
         </is>
       </c>
     </row>
@@ -7127,7 +7724,7 @@
       </c>
       <c r="F22" s="56" t="inlineStr">
         <is>
-          <t>A complete guide to strain gauges: how they work, the main types (foil, wire, semiconductor, vibrating wire), the gauge factor formula, and where they're used in structural monitoring.</t>
+          <t>A guide to strain gauges: how they work, the main types (foil, wire, semiconductor, vibrating wire), the gauge factor formula, and structural monitoring uses.</t>
         </is>
       </c>
       <c r="G22" s="55" t="n">
@@ -7148,7 +7745,7 @@
       </c>
       <c r="K22" s="56" t="inlineStr">
         <is>
-          <t>A complete guide to strain gauges: how they work, the main types (foil, wire, semiconductor, vibrating wire), the gauge factor formula, and where they're used in structural monitoring.</t>
+          <t>A guide to strain gauges: how they work, the main types (foil, wire, semiconductor, vibrating wire), the gauge factor formula, and structural monitoring uses.</t>
         </is>
       </c>
       <c r="L22" s="55" t="inlineStr">
@@ -7158,12 +7755,12 @@
       </c>
       <c r="M22" s="55" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N22" s="56" t="inlineStr">
         <is>
-          <t>Title 63 chars (&gt;60); Meta 184 chars (&gt;160)</t>
+          <t>Title 63 chars (&gt;60) - not addressed (Ahrefs SEO audit only flagged titles &gt;70 chars); Meta description fixed 2026-08-15 (158 chars)</t>
         </is>
       </c>
     </row>
@@ -7186,12 +7783,12 @@
       <c r="D23" s="55" t="inlineStr"/>
       <c r="E23" s="56" t="inlineStr">
         <is>
-          <t>What Is an Accelerometer Sensor? Working Principle, Types &amp; Applications</t>
+          <t>What Is an Accelerometer Sensor? Types &amp; Applications</t>
         </is>
       </c>
       <c r="F23" s="56" t="inlineStr">
         <is>
-          <t>How accelerometer sensors work, the difference between piezoelectric, capacitive MEMS and tri-axial types, and how they're used for seismic, structural and machinery monitoring.</t>
+          <t>How accelerometer sensors work, piezoelectric vs capacitive MEMS types, and how they're used for seismic, structural and machinery monitoring.</t>
         </is>
       </c>
       <c r="G23" s="55" t="n">
@@ -7207,12 +7804,12 @@
       </c>
       <c r="J23" s="56" t="inlineStr">
         <is>
-          <t>What Is an Accelerometer Sensor? Working Principle, Types &amp; Applications</t>
+          <t>What Is an Accelerometer Sensor? Types &amp; Applications</t>
         </is>
       </c>
       <c r="K23" s="56" t="inlineStr">
         <is>
-          <t>How accelerometer sensors work, the difference between piezoelectric, capacitive MEMS and tri-axial types, and how they're used for seismic, structural and machinery monitoring.</t>
+          <t>How accelerometer sensors work, piezoelectric vs capacitive MEMS types, and how they're used for seismic, structural and machinery monitoring.</t>
         </is>
       </c>
       <c r="L23" s="55" t="inlineStr">
@@ -7222,12 +7819,12 @@
       </c>
       <c r="M23" s="55" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N23" s="56" t="inlineStr">
         <is>
-          <t>Title 72 chars (&gt;60); Meta 177 chars (&gt;160)</t>
+          <t>Meta description fixed 2026-08-15 (142 chars); Title fixed 2026-08-15 (53 chars)</t>
         </is>
       </c>
     </row>
@@ -7255,7 +7852,7 @@
       </c>
       <c r="F24" s="56" t="inlineStr">
         <is>
-          <t>How digital inclinometers and tiltmeters measure tilt and rotation, the difference between the two terms, and where they're used in slope, structural and rail monitoring.</t>
+          <t>How digital inclinometers and tiltmeters measure tilt and rotation, the difference between the two, and their use in slope and structural monitoring.</t>
         </is>
       </c>
       <c r="G24" s="55" t="n">
@@ -7276,7 +7873,7 @@
       </c>
       <c r="K24" s="56" t="inlineStr">
         <is>
-          <t>How digital inclinometers and tiltmeters measure tilt and rotation, the difference between the two terms, and where they're used in slope, structural and rail monitoring.</t>
+          <t>How digital inclinometers and tiltmeters measure tilt and rotation, the difference between the two, and their use in slope and structural monitoring.</t>
         </is>
       </c>
       <c r="L24" s="55" t="inlineStr">
@@ -7286,12 +7883,12 @@
       </c>
       <c r="M24" s="55" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N24" s="56" t="inlineStr">
         <is>
-          <t>Meta 170 chars (&gt;160)</t>
+          <t>Meta description fixed 2026-08-15 (149 chars)</t>
         </is>
       </c>
     </row>
@@ -9039,7 +9636,7 @@
       </c>
       <c r="F53" s="56" t="inlineStr">
         <is>
-          <t>LCC by XGRIDS — capture, create and share 3D Gaussian Splatting models. LCC Studio, LCC Cloud, Model Editor, Scene Editor and cross-platform SDKs, available in India via Sentra, official XGRIDS reseller.</t>
+          <t>LCC by XGRIDS — capture, create and share 3D Gaussian Splatting models with Studio, Cloud, Model &amp; Scene Editor, available in India via Sentra.</t>
         </is>
       </c>
       <c r="G53" s="55" t="n">
@@ -9070,12 +9667,12 @@
       </c>
       <c r="M53" s="55" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N53" s="56" t="inlineStr">
         <is>
-          <t>Title 62 chars (&gt;60); Meta 203 chars (&gt;160)</t>
+          <t>Title 62 chars (&gt;60) - not addressed (Ahrefs SEO audit only flagged titles &gt;70 chars); Meta description fixed 2026-08-15 (143 chars)</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9824,7 @@
       </c>
       <c r="F56" s="56" t="inlineStr">
         <is>
-          <t>LixelStudio by XGRIDS — one-click processing from raw scan data to production-ready point clouds. SLAM mapping, map fusion, measurement tools and BIM/CAD/GIS export, available in India via Sentra, official XGRIDS reseller.</t>
+          <t>LixelStudio by XGRIDS — one-click processing from raw scan data to production-ready point clouds, with SLAM mapping and BIM/CAD/GIS export, via Sentra.</t>
         </is>
       </c>
       <c r="G56" s="55" t="n">
@@ -9258,12 +9855,12 @@
       </c>
       <c r="M56" s="55" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N56" s="56" t="inlineStr">
         <is>
-          <t>Title 66 chars (&gt;60); Meta 222 chars (&gt;160)</t>
+          <t>Title 66 chars (&gt;60) - not addressed (Ahrefs SEO audit only flagged titles &gt;70 chars); Meta description fixed 2026-08-15 (151 chars)</t>
         </is>
       </c>
     </row>
@@ -10670,6 +11267,4091 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J110"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="57" t="inlineStr">
+        <is>
+          <t>Sentra SEO Growth Plan — 90-Day Action Plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="58" t="inlineStr">
+        <is>
+          <t>Built from the Ahrefs overview reviewed on 2026-08-15. Primary objective: raise Domain Rating (DR) through higher-quality referring domains, fix technical issues, and grow organic indexing/traffic. Review and update Status weekly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="59" t="inlineStr">
+        <is>
+          <t>Baseline (as of 2026-08-15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="60" t="inlineStr">
+        <is>
+          <t>Domain Rating (DR)</t>
+        </is>
+      </c>
+      <c r="B5" s="61" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="C5" s="62" t="n"/>
+      <c r="D5" s="62" t="n"/>
+      <c r="E5" s="63" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="60" t="inlineStr">
+        <is>
+          <t>URL Rating (UR)</t>
+        </is>
+      </c>
+      <c r="B6" s="61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C6" s="62" t="n"/>
+      <c r="D6" s="62" t="n"/>
+      <c r="E6" s="63" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="60" t="inlineStr">
+        <is>
+          <t>Backlinks</t>
+        </is>
+      </c>
+      <c r="B7" s="61" t="inlineStr">
+        <is>
+          <t>167 (+5 last 24h)</t>
+        </is>
+      </c>
+      <c r="C7" s="62" t="n"/>
+      <c r="D7" s="62" t="n"/>
+      <c r="E7" s="63" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="60" t="inlineStr">
+        <is>
+          <t>Referring domains</t>
+        </is>
+      </c>
+      <c r="B8" s="61" t="inlineStr">
+        <is>
+          <t>149 (+5 last 24h)</t>
+        </is>
+      </c>
+      <c r="C8" s="62" t="n"/>
+      <c r="D8" s="62" t="n"/>
+      <c r="E8" s="63" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="60" t="inlineStr">
+        <is>
+          <t>Referring domains with DR 10+</t>
+        </is>
+      </c>
+      <c r="B9" s="61" t="inlineStr">
+        <is>
+          <t>0% — every linking domain is DR 0–9 (root cause of low DR)</t>
+        </is>
+      </c>
+      <c r="C9" s="62" t="n"/>
+      <c r="D9" s="62" t="n"/>
+      <c r="E9" s="63" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="60" t="inlineStr">
+        <is>
+          <t>Nofollow share</t>
+        </is>
+      </c>
+      <c r="B10" s="61" t="inlineStr">
+        <is>
+          <t>92.6% of referring domains / 92.8% of backlinks are nofollow</t>
+        </is>
+      </c>
+      <c r="C10" s="62" t="n"/>
+      <c r="D10" s="62" t="n"/>
+      <c r="E10" s="63" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="60" t="inlineStr">
+        <is>
+          <t>Organic keywords ranking</t>
+        </is>
+      </c>
+      <c r="B11" s="61" t="inlineStr">
+        <is>
+          <t>1 (0 in top 3)</t>
+        </is>
+      </c>
+      <c r="C11" s="62" t="n"/>
+      <c r="D11" s="62" t="n"/>
+      <c r="E11" s="63" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="60" t="inlineStr">
+        <is>
+          <t>Organic traffic / value</t>
+        </is>
+      </c>
+      <c r="B12" s="61" t="inlineStr">
+        <is>
+          <t>0 / $0</t>
+        </is>
+      </c>
+      <c r="C12" s="62" t="n"/>
+      <c r="D12" s="62" t="n"/>
+      <c r="E12" s="63" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="60" t="inlineStr">
+        <is>
+          <t>Crawled pages returning 404</t>
+        </is>
+      </c>
+      <c r="B13" s="61" t="inlineStr">
+        <is>
+          <t>8 of 98 (8.2%)</t>
+        </is>
+      </c>
+      <c r="C13" s="62" t="n"/>
+      <c r="D13" s="62" t="n"/>
+      <c r="E13" s="63" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="59" t="inlineStr">
+        <is>
+          <t>90-Day Targets</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="64" t="inlineStr">
+        <is>
+          <t>Day 30 target</t>
+        </is>
+      </c>
+      <c r="B16" s="65" t="inlineStr">
+        <is>
+          <t>All 8 broken pages fixed (redirect/restore/delink); outreach sent to all 5 named partner contacts; 2 guest-post pitches sent; GSC + sitemap indexing verified; baseline logged below weekly.</t>
+        </is>
+      </c>
+      <c r="C16" s="62" t="n"/>
+      <c r="D16" s="62" t="n"/>
+      <c r="E16" s="63" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="64" t="inlineStr">
+        <is>
+          <t>Day 60 target</t>
+        </is>
+      </c>
+      <c r="B17" s="65" t="inlineStr">
+        <is>
+          <t>≥3 new referring domains at DR 20+; ≥1 guest post published with a dofollow link; government/PSU outreach opened with ≥3 contacts (Railways, CRDA, SAIL/BWSSB/APTIDCO).</t>
+        </is>
+      </c>
+      <c r="C17" s="62" t="n"/>
+      <c r="D17" s="62" t="n"/>
+      <c r="E17" s="63" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="64" t="inlineStr">
+        <is>
+          <t>Day 90 target</t>
+        </is>
+      </c>
+      <c r="B18" s="65" t="inlineStr">
+        <is>
+          <t>DR moved from 1.2 into the ~4–8 range (realistic, not overhyped — DR growth is logarithmic); ≥5 new dofollow referring domains at DR 20+; organic keywords &gt;10; 404 rate at 0%; nofollow share reduced from 92%.</t>
+        </is>
+      </c>
+      <c r="C18" s="62" t="n"/>
+      <c r="D18" s="62" t="n"/>
+      <c r="E18" s="63" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="66" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B20" s="66" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C20" s="66" t="inlineStr">
+        <is>
+          <t>Month Phase</t>
+        </is>
+      </c>
+      <c r="D20" s="66" t="inlineStr">
+        <is>
+          <t>Focus Area</t>
+        </is>
+      </c>
+      <c r="E20" s="66" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="F20" s="66" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="G20" s="66" t="inlineStr">
+        <is>
+          <t>Target / KPI</t>
+        </is>
+      </c>
+      <c r="H20" s="66" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="I20" s="66" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J20" s="66" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="67" t="inlineStr">
+        <is>
+          <t>2026-08-17 (Mon)</t>
+        </is>
+      </c>
+      <c r="C21" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D21" s="68" t="inlineStr">
+        <is>
+          <t>Backlink Outreach</t>
+        </is>
+      </c>
+      <c r="E21" s="68" t="inlineStr">
+        <is>
+          <t>Send/follow up outreach: XGRIDS (official India reseller — request partner/reseller-page backlink)</t>
+        </is>
+      </c>
+      <c r="F21" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G21" s="68" t="inlineStr">
+        <is>
+          <t>1 personalized email + LinkedIn touch; log response in Change Log</t>
+        </is>
+      </c>
+      <c r="H21" s="67" t="inlineStr"/>
+      <c r="I21" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J21" s="68" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="67" t="inlineStr">
+        <is>
+          <t>2026-08-18 (Tue)</t>
+        </is>
+      </c>
+      <c r="C22" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D22" s="68" t="inlineStr">
+        <is>
+          <t>Technical SEO</t>
+        </is>
+      </c>
+      <c r="E22" s="68" t="inlineStr">
+        <is>
+          <t>Audit indexing status, 404s, canonical tags, sitemap and schema for a batch of 10 pages; fix any issues found</t>
+        </is>
+      </c>
+      <c r="F22" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G22" s="68" t="inlineStr">
+        <is>
+          <t>0 broken links/pages in the batch reviewed</t>
+        </is>
+      </c>
+      <c r="H22" s="67" t="inlineStr"/>
+      <c r="I22" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J22" s="68" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="67" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="67" t="inlineStr">
+        <is>
+          <t>2026-08-19 (Wed)</t>
+        </is>
+      </c>
+      <c r="C23" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D23" s="68" t="inlineStr">
+        <is>
+          <t>On-Page SEO</t>
+        </is>
+      </c>
+      <c r="E23" s="68" t="inlineStr">
+        <is>
+          <t>Review keyword targeting, internal linking, title/meta length for a batch of pages in SEO Tracker; update as needed</t>
+        </is>
+      </c>
+      <c r="F23" s="67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G23" s="68" t="inlineStr">
+        <is>
+          <t>All titles ≤60 chars, meta ≤155 chars, ≥3 internal links per page</t>
+        </is>
+      </c>
+      <c r="H23" s="67" t="inlineStr"/>
+      <c r="I23" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J23" s="68" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="67" t="inlineStr">
+        <is>
+          <t>2026-08-20 (Thu)</t>
+        </is>
+      </c>
+      <c r="C24" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D24" s="68" t="inlineStr">
+        <is>
+          <t>PR / Guest Posting</t>
+        </is>
+      </c>
+      <c r="E24" s="68" t="inlineStr">
+        <is>
+          <t>Pitch or draft one guest article / press story (AICCC, BridgePulse, or a technical SHM/fatigue piece repurposed for a trade publication)</t>
+        </is>
+      </c>
+      <c r="F24" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G24" s="68" t="inlineStr">
+        <is>
+          <t>1 pitch sent or 1 draft completed</t>
+        </is>
+      </c>
+      <c r="H24" s="67" t="inlineStr"/>
+      <c r="I24" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J24" s="68" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="67" t="inlineStr">
+        <is>
+          <t>2026-08-21 (Fri)</t>
+        </is>
+      </c>
+      <c r="C25" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D25" s="68" t="inlineStr">
+        <is>
+          <t>Tracking &amp; Reporting</t>
+        </is>
+      </c>
+      <c r="E25" s="68" t="inlineStr">
+        <is>
+          <t>Update DR/backlink/referring-domain snapshot; check Google Search Console for indexing and query changes; log results in this sheet</t>
+        </is>
+      </c>
+      <c r="F25" s="67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G25" s="68" t="inlineStr">
+        <is>
+          <t>Weekly metrics logged; Status column updated for the week</t>
+        </is>
+      </c>
+      <c r="H25" s="67" t="inlineStr"/>
+      <c r="I25" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J25" s="68" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="67" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="67" t="inlineStr">
+        <is>
+          <t>2026-08-22 (Sat)</t>
+        </is>
+      </c>
+      <c r="C26" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D26" s="68" t="inlineStr">
+        <is>
+          <t>Content Prep</t>
+        </is>
+      </c>
+      <c r="E26" s="68" t="inlineStr">
+        <is>
+          <t>Batch-draft or repurpose content for next week's guest post / PR pitch / internal linking pass</t>
+        </is>
+      </c>
+      <c r="F26" s="67" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G26" s="68" t="inlineStr">
+        <is>
+          <t>1 draft asset queued</t>
+        </is>
+      </c>
+      <c r="H26" s="67" t="inlineStr"/>
+      <c r="I26" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J26" s="68" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="67" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="67" t="inlineStr">
+        <is>
+          <t>2026-08-23 (Sun)</t>
+        </is>
+      </c>
+      <c r="C27" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D27" s="68" t="inlineStr">
+        <is>
+          <t>Buffer</t>
+        </is>
+      </c>
+      <c r="E27" s="68" t="inlineStr">
+        <is>
+          <t>No scheduled outreach — buffer day / catch up on any slipped tasks</t>
+        </is>
+      </c>
+      <c r="F27" s="67" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G27" s="68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H27" s="67" t="inlineStr"/>
+      <c r="I27" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J27" s="68" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="67" t="n">
+        <v>8</v>
+      </c>
+      <c r="B28" s="67" t="inlineStr">
+        <is>
+          <t>2026-08-24 (Mon)</t>
+        </is>
+      </c>
+      <c r="C28" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D28" s="68" t="inlineStr">
+        <is>
+          <t>Backlink Outreach</t>
+        </is>
+      </c>
+      <c r="E28" s="68" t="inlineStr">
+        <is>
+          <t>Send/follow up outreach: Worldsensing (Track to the Future collaboration — request article/partner backlink)</t>
+        </is>
+      </c>
+      <c r="F28" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G28" s="68" t="inlineStr">
+        <is>
+          <t>1 personalized email + LinkedIn touch; log response in Change Log</t>
+        </is>
+      </c>
+      <c r="H28" s="67" t="inlineStr"/>
+      <c r="I28" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J28" s="68" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="67" t="n">
+        <v>9</v>
+      </c>
+      <c r="B29" s="67" t="inlineStr">
+        <is>
+          <t>2026-08-25 (Tue)</t>
+        </is>
+      </c>
+      <c r="C29" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D29" s="68" t="inlineStr">
+        <is>
+          <t>Technical SEO</t>
+        </is>
+      </c>
+      <c r="E29" s="68" t="inlineStr">
+        <is>
+          <t>Audit indexing status, 404s, canonical tags, sitemap and schema for a batch of 10 pages; fix any issues found</t>
+        </is>
+      </c>
+      <c r="F29" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G29" s="68" t="inlineStr">
+        <is>
+          <t>0 broken links/pages in the batch reviewed</t>
+        </is>
+      </c>
+      <c r="H29" s="67" t="inlineStr"/>
+      <c r="I29" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J29" s="68" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="67" t="n">
+        <v>10</v>
+      </c>
+      <c r="B30" s="67" t="inlineStr">
+        <is>
+          <t>2026-08-26 (Wed)</t>
+        </is>
+      </c>
+      <c r="C30" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D30" s="68" t="inlineStr">
+        <is>
+          <t>On-Page SEO</t>
+        </is>
+      </c>
+      <c r="E30" s="68" t="inlineStr">
+        <is>
+          <t>Review keyword targeting, internal linking, title/meta length for a batch of pages in SEO Tracker; update as needed</t>
+        </is>
+      </c>
+      <c r="F30" s="67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G30" s="68" t="inlineStr">
+        <is>
+          <t>All titles ≤60 chars, meta ≤155 chars, ≥3 internal links per page</t>
+        </is>
+      </c>
+      <c r="H30" s="67" t="inlineStr"/>
+      <c r="I30" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J30" s="68" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="67" t="n">
+        <v>11</v>
+      </c>
+      <c r="B31" s="67" t="inlineStr">
+        <is>
+          <t>2026-08-27 (Thu)</t>
+        </is>
+      </c>
+      <c r="C31" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D31" s="68" t="inlineStr">
+        <is>
+          <t>PR / Guest Posting</t>
+        </is>
+      </c>
+      <c r="E31" s="68" t="inlineStr">
+        <is>
+          <t>Pitch or draft one guest article / press story (AICCC, BridgePulse, or a technical SHM/fatigue piece repurposed for a trade publication)</t>
+        </is>
+      </c>
+      <c r="F31" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G31" s="68" t="inlineStr">
+        <is>
+          <t>1 pitch sent or 1 draft completed</t>
+        </is>
+      </c>
+      <c r="H31" s="67" t="inlineStr"/>
+      <c r="I31" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J31" s="68" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="67" t="n">
+        <v>12</v>
+      </c>
+      <c r="B32" s="67" t="inlineStr">
+        <is>
+          <t>2026-08-28 (Fri)</t>
+        </is>
+      </c>
+      <c r="C32" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D32" s="68" t="inlineStr">
+        <is>
+          <t>Tracking &amp; Reporting</t>
+        </is>
+      </c>
+      <c r="E32" s="68" t="inlineStr">
+        <is>
+          <t>Update DR/backlink/referring-domain snapshot; check Google Search Console for indexing and query changes; log results in this sheet</t>
+        </is>
+      </c>
+      <c r="F32" s="67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G32" s="68" t="inlineStr">
+        <is>
+          <t>Weekly metrics logged; Status column updated for the week</t>
+        </is>
+      </c>
+      <c r="H32" s="67" t="inlineStr"/>
+      <c r="I32" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J32" s="68" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="67" t="n">
+        <v>13</v>
+      </c>
+      <c r="B33" s="67" t="inlineStr">
+        <is>
+          <t>2026-08-29 (Sat)</t>
+        </is>
+      </c>
+      <c r="C33" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D33" s="68" t="inlineStr">
+        <is>
+          <t>Content Prep</t>
+        </is>
+      </c>
+      <c r="E33" s="68" t="inlineStr">
+        <is>
+          <t>Batch-draft or repurpose content for next week's guest post / PR pitch / internal linking pass</t>
+        </is>
+      </c>
+      <c r="F33" s="67" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G33" s="68" t="inlineStr">
+        <is>
+          <t>1 draft asset queued</t>
+        </is>
+      </c>
+      <c r="H33" s="67" t="inlineStr"/>
+      <c r="I33" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J33" s="68" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="67" t="n">
+        <v>14</v>
+      </c>
+      <c r="B34" s="67" t="inlineStr">
+        <is>
+          <t>2026-08-30 (Sun)</t>
+        </is>
+      </c>
+      <c r="C34" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D34" s="68" t="inlineStr">
+        <is>
+          <t>Buffer</t>
+        </is>
+      </c>
+      <c r="E34" s="68" t="inlineStr">
+        <is>
+          <t>No scheduled outreach — buffer day / catch up on any slipped tasks</t>
+        </is>
+      </c>
+      <c r="F34" s="67" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G34" s="68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H34" s="67" t="inlineStr"/>
+      <c r="I34" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J34" s="68" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="67" t="n">
+        <v>15</v>
+      </c>
+      <c r="B35" s="67" t="inlineStr">
+        <is>
+          <t>2026-08-31 (Mon)</t>
+        </is>
+      </c>
+      <c r="C35" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D35" s="68" t="inlineStr">
+        <is>
+          <t>Backlink Outreach</t>
+        </is>
+      </c>
+      <c r="E35" s="68" t="inlineStr">
+        <is>
+          <t>Send/follow up outreach: DYWIDAG (Track to the Future co-host — request case-study backlink)</t>
+        </is>
+      </c>
+      <c r="F35" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G35" s="68" t="inlineStr">
+        <is>
+          <t>1 personalized email + LinkedIn touch; log response in Change Log</t>
+        </is>
+      </c>
+      <c r="H35" s="67" t="inlineStr"/>
+      <c r="I35" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J35" s="68" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="67" t="n">
+        <v>16</v>
+      </c>
+      <c r="B36" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-01 (Tue)</t>
+        </is>
+      </c>
+      <c r="C36" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D36" s="68" t="inlineStr">
+        <is>
+          <t>Technical SEO</t>
+        </is>
+      </c>
+      <c r="E36" s="68" t="inlineStr">
+        <is>
+          <t>Audit indexing status, 404s, canonical tags, sitemap and schema for a batch of 10 pages; fix any issues found</t>
+        </is>
+      </c>
+      <c r="F36" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G36" s="68" t="inlineStr">
+        <is>
+          <t>0 broken links/pages in the batch reviewed</t>
+        </is>
+      </c>
+      <c r="H36" s="67" t="inlineStr"/>
+      <c r="I36" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J36" s="68" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="67" t="n">
+        <v>17</v>
+      </c>
+      <c r="B37" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-02 (Wed)</t>
+        </is>
+      </c>
+      <c r="C37" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D37" s="68" t="inlineStr">
+        <is>
+          <t>On-Page SEO</t>
+        </is>
+      </c>
+      <c r="E37" s="68" t="inlineStr">
+        <is>
+          <t>Review keyword targeting, internal linking, title/meta length for a batch of pages in SEO Tracker; update as needed</t>
+        </is>
+      </c>
+      <c r="F37" s="67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G37" s="68" t="inlineStr">
+        <is>
+          <t>All titles ≤60 chars, meta ≤155 chars, ≥3 internal links per page</t>
+        </is>
+      </c>
+      <c r="H37" s="67" t="inlineStr"/>
+      <c r="I37" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J37" s="68" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="67" t="n">
+        <v>18</v>
+      </c>
+      <c r="B38" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-03 (Thu)</t>
+        </is>
+      </c>
+      <c r="C38" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D38" s="68" t="inlineStr">
+        <is>
+          <t>PR / Guest Posting</t>
+        </is>
+      </c>
+      <c r="E38" s="68" t="inlineStr">
+        <is>
+          <t>Pitch or draft one guest article / press story (AICCC, BridgePulse, or a technical SHM/fatigue piece repurposed for a trade publication)</t>
+        </is>
+      </c>
+      <c r="F38" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G38" s="68" t="inlineStr">
+        <is>
+          <t>1 pitch sent or 1 draft completed</t>
+        </is>
+      </c>
+      <c r="H38" s="67" t="inlineStr"/>
+      <c r="I38" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J38" s="68" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="67" t="n">
+        <v>19</v>
+      </c>
+      <c r="B39" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-04 (Fri)</t>
+        </is>
+      </c>
+      <c r="C39" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D39" s="68" t="inlineStr">
+        <is>
+          <t>Tracking &amp; Reporting</t>
+        </is>
+      </c>
+      <c r="E39" s="68" t="inlineStr">
+        <is>
+          <t>Update DR/backlink/referring-domain snapshot; check Google Search Console for indexing and query changes; log results in this sheet</t>
+        </is>
+      </c>
+      <c r="F39" s="67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G39" s="68" t="inlineStr">
+        <is>
+          <t>Weekly metrics logged; Status column updated for the week</t>
+        </is>
+      </c>
+      <c r="H39" s="67" t="inlineStr"/>
+      <c r="I39" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J39" s="68" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="67" t="n">
+        <v>20</v>
+      </c>
+      <c r="B40" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-05 (Sat)</t>
+        </is>
+      </c>
+      <c r="C40" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D40" s="68" t="inlineStr">
+        <is>
+          <t>Content Prep</t>
+        </is>
+      </c>
+      <c r="E40" s="68" t="inlineStr">
+        <is>
+          <t>Batch-draft or repurpose content for next week's guest post / PR pitch / internal linking pass</t>
+        </is>
+      </c>
+      <c r="F40" s="67" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G40" s="68" t="inlineStr">
+        <is>
+          <t>1 draft asset queued</t>
+        </is>
+      </c>
+      <c r="H40" s="67" t="inlineStr"/>
+      <c r="I40" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J40" s="68" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="67" t="n">
+        <v>21</v>
+      </c>
+      <c r="B41" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-06 (Sun)</t>
+        </is>
+      </c>
+      <c r="C41" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D41" s="68" t="inlineStr">
+        <is>
+          <t>Buffer</t>
+        </is>
+      </c>
+      <c r="E41" s="68" t="inlineStr">
+        <is>
+          <t>No scheduled outreach — buffer day / catch up on any slipped tasks</t>
+        </is>
+      </c>
+      <c r="F41" s="67" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G41" s="68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="67" t="inlineStr"/>
+      <c r="I41" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J41" s="68" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="67" t="n">
+        <v>22</v>
+      </c>
+      <c r="B42" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-07 (Mon)</t>
+        </is>
+      </c>
+      <c r="C42" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D42" s="68" t="inlineStr">
+        <is>
+          <t>Backlink Outreach</t>
+        </is>
+      </c>
+      <c r="E42" s="68" t="inlineStr">
+        <is>
+          <t>Send/follow up outreach: Clove Technologies (parent company — audit &amp; confirm dofollow cross-linking both directions)</t>
+        </is>
+      </c>
+      <c r="F42" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G42" s="68" t="inlineStr">
+        <is>
+          <t>1 personalized email + LinkedIn touch; log response in Change Log</t>
+        </is>
+      </c>
+      <c r="H42" s="67" t="inlineStr"/>
+      <c r="I42" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J42" s="68" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="67" t="n">
+        <v>23</v>
+      </c>
+      <c r="B43" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-08 (Tue)</t>
+        </is>
+      </c>
+      <c r="C43" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D43" s="68" t="inlineStr">
+        <is>
+          <t>Technical SEO</t>
+        </is>
+      </c>
+      <c r="E43" s="68" t="inlineStr">
+        <is>
+          <t>Audit indexing status, 404s, canonical tags, sitemap and schema for a batch of 10 pages; fix any issues found</t>
+        </is>
+      </c>
+      <c r="F43" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G43" s="68" t="inlineStr">
+        <is>
+          <t>0 broken links/pages in the batch reviewed</t>
+        </is>
+      </c>
+      <c r="H43" s="67" t="inlineStr"/>
+      <c r="I43" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J43" s="68" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="67" t="n">
+        <v>24</v>
+      </c>
+      <c r="B44" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-09 (Wed)</t>
+        </is>
+      </c>
+      <c r="C44" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D44" s="68" t="inlineStr">
+        <is>
+          <t>On-Page SEO</t>
+        </is>
+      </c>
+      <c r="E44" s="68" t="inlineStr">
+        <is>
+          <t>Review keyword targeting, internal linking, title/meta length for a batch of pages in SEO Tracker; update as needed</t>
+        </is>
+      </c>
+      <c r="F44" s="67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G44" s="68" t="inlineStr">
+        <is>
+          <t>All titles ≤60 chars, meta ≤155 chars, ≥3 internal links per page</t>
+        </is>
+      </c>
+      <c r="H44" s="67" t="inlineStr"/>
+      <c r="I44" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J44" s="68" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="67" t="n">
+        <v>25</v>
+      </c>
+      <c r="B45" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-10 (Thu)</t>
+        </is>
+      </c>
+      <c r="C45" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D45" s="68" t="inlineStr">
+        <is>
+          <t>PR / Guest Posting</t>
+        </is>
+      </c>
+      <c r="E45" s="68" t="inlineStr">
+        <is>
+          <t>Pitch or draft one guest article / press story (AICCC, BridgePulse, or a technical SHM/fatigue piece repurposed for a trade publication)</t>
+        </is>
+      </c>
+      <c r="F45" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G45" s="68" t="inlineStr">
+        <is>
+          <t>1 pitch sent or 1 draft completed</t>
+        </is>
+      </c>
+      <c r="H45" s="67" t="inlineStr"/>
+      <c r="I45" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J45" s="68" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="67" t="n">
+        <v>26</v>
+      </c>
+      <c r="B46" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-11 (Fri)</t>
+        </is>
+      </c>
+      <c r="C46" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D46" s="68" t="inlineStr">
+        <is>
+          <t>Tracking &amp; Reporting</t>
+        </is>
+      </c>
+      <c r="E46" s="68" t="inlineStr">
+        <is>
+          <t>Update DR/backlink/referring-domain snapshot; check Google Search Console for indexing and query changes; log results in this sheet</t>
+        </is>
+      </c>
+      <c r="F46" s="67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G46" s="68" t="inlineStr">
+        <is>
+          <t>Weekly metrics logged; Status column updated for the week</t>
+        </is>
+      </c>
+      <c r="H46" s="67" t="inlineStr"/>
+      <c r="I46" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J46" s="68" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="67" t="n">
+        <v>27</v>
+      </c>
+      <c r="B47" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-12 (Sat)</t>
+        </is>
+      </c>
+      <c r="C47" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D47" s="68" t="inlineStr">
+        <is>
+          <t>Content Prep</t>
+        </is>
+      </c>
+      <c r="E47" s="68" t="inlineStr">
+        <is>
+          <t>Batch-draft or repurpose content for next week's guest post / PR pitch / internal linking pass</t>
+        </is>
+      </c>
+      <c r="F47" s="67" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G47" s="68" t="inlineStr">
+        <is>
+          <t>1 draft asset queued</t>
+        </is>
+      </c>
+      <c r="H47" s="67" t="inlineStr"/>
+      <c r="I47" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J47" s="68" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="67" t="n">
+        <v>28</v>
+      </c>
+      <c r="B48" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-13 (Sun)</t>
+        </is>
+      </c>
+      <c r="C48" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D48" s="68" t="inlineStr">
+        <is>
+          <t>Buffer</t>
+        </is>
+      </c>
+      <c r="E48" s="68" t="inlineStr">
+        <is>
+          <t>No scheduled outreach — buffer day / catch up on any slipped tasks</t>
+        </is>
+      </c>
+      <c r="F48" s="67" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G48" s="68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="67" t="inlineStr"/>
+      <c r="I48" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J48" s="68" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="67" t="n">
+        <v>29</v>
+      </c>
+      <c r="B49" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-14 (Mon)</t>
+        </is>
+      </c>
+      <c r="C49" s="67" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D49" s="68" t="inlineStr">
+        <is>
+          <t>Backlink Outreach</t>
+        </is>
+      </c>
+      <c r="E49" s="68" t="inlineStr">
+        <is>
+          <t>Send/follow up outreach: Indian Railways – Northern Railway (request project/vendor mention with link)</t>
+        </is>
+      </c>
+      <c r="F49" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G49" s="68" t="inlineStr">
+        <is>
+          <t>1 personalized email + LinkedIn touch; log response in Change Log</t>
+        </is>
+      </c>
+      <c r="H49" s="67" t="inlineStr"/>
+      <c r="I49" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J49" s="68" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="70" t="n">
+        <v>30</v>
+      </c>
+      <c r="B50" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-15 (Tue)</t>
+        </is>
+      </c>
+      <c r="C50" s="70" t="inlineStr">
+        <is>
+          <t>Month 1 — Foundation</t>
+        </is>
+      </c>
+      <c r="D50" s="71" t="inlineStr">
+        <is>
+          <t>Milestone Review</t>
+        </is>
+      </c>
+      <c r="E50" s="71" t="inlineStr">
+        <is>
+          <t>Month 1 review: confirm all targets met (404s fixed, 5 partner outreach sent, 2 pitches sent, GSC/sitemap verified). Reset priorities for Month 2 based on responses received.</t>
+        </is>
+      </c>
+      <c r="F50" s="70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G50" s="71" t="inlineStr">
+        <is>
+          <t>Month checkpoint completed and documented</t>
+        </is>
+      </c>
+      <c r="H50" s="70" t="inlineStr"/>
+      <c r="I50" s="70" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J50" s="71" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="67" t="n">
+        <v>31</v>
+      </c>
+      <c r="B51" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-16 (Wed)</t>
+        </is>
+      </c>
+      <c r="C51" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D51" s="68" t="inlineStr">
+        <is>
+          <t>On-Page SEO</t>
+        </is>
+      </c>
+      <c r="E51" s="68" t="inlineStr">
+        <is>
+          <t>Review keyword targeting, internal linking, title/meta length for a batch of pages in SEO Tracker; update as needed</t>
+        </is>
+      </c>
+      <c r="F51" s="67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G51" s="68" t="inlineStr">
+        <is>
+          <t>All titles ≤60 chars, meta ≤155 chars, ≥3 internal links per page</t>
+        </is>
+      </c>
+      <c r="H51" s="67" t="inlineStr"/>
+      <c r="I51" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J51" s="68" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="67" t="n">
+        <v>32</v>
+      </c>
+      <c r="B52" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-17 (Thu)</t>
+        </is>
+      </c>
+      <c r="C52" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D52" s="68" t="inlineStr">
+        <is>
+          <t>PR / Guest Posting</t>
+        </is>
+      </c>
+      <c r="E52" s="68" t="inlineStr">
+        <is>
+          <t>Pitch or draft one guest article / press story (AICCC, BridgePulse, or a technical SHM/fatigue piece repurposed for a trade publication)</t>
+        </is>
+      </c>
+      <c r="F52" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G52" s="68" t="inlineStr">
+        <is>
+          <t>1 pitch sent or 1 draft completed</t>
+        </is>
+      </c>
+      <c r="H52" s="67" t="inlineStr"/>
+      <c r="I52" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J52" s="68" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="67" t="n">
+        <v>33</v>
+      </c>
+      <c r="B53" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-18 (Fri)</t>
+        </is>
+      </c>
+      <c r="C53" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D53" s="68" t="inlineStr">
+        <is>
+          <t>Tracking &amp; Reporting</t>
+        </is>
+      </c>
+      <c r="E53" s="68" t="inlineStr">
+        <is>
+          <t>Update DR/backlink/referring-domain snapshot; check Google Search Console for indexing and query changes; log results in this sheet</t>
+        </is>
+      </c>
+      <c r="F53" s="67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G53" s="68" t="inlineStr">
+        <is>
+          <t>Weekly metrics logged; Status column updated for the week</t>
+        </is>
+      </c>
+      <c r="H53" s="67" t="inlineStr"/>
+      <c r="I53" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J53" s="68" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="67" t="n">
+        <v>34</v>
+      </c>
+      <c r="B54" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-19 (Sat)</t>
+        </is>
+      </c>
+      <c r="C54" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D54" s="68" t="inlineStr">
+        <is>
+          <t>Content Prep</t>
+        </is>
+      </c>
+      <c r="E54" s="68" t="inlineStr">
+        <is>
+          <t>Batch-draft or repurpose content for next week's guest post / PR pitch / internal linking pass</t>
+        </is>
+      </c>
+      <c r="F54" s="67" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G54" s="68" t="inlineStr">
+        <is>
+          <t>1 draft asset queued</t>
+        </is>
+      </c>
+      <c r="H54" s="67" t="inlineStr"/>
+      <c r="I54" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J54" s="68" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="67" t="n">
+        <v>35</v>
+      </c>
+      <c r="B55" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-20 (Sun)</t>
+        </is>
+      </c>
+      <c r="C55" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D55" s="68" t="inlineStr">
+        <is>
+          <t>Buffer</t>
+        </is>
+      </c>
+      <c r="E55" s="68" t="inlineStr">
+        <is>
+          <t>No scheduled outreach — buffer day / catch up on any slipped tasks</t>
+        </is>
+      </c>
+      <c r="F55" s="67" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G55" s="68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" s="67" t="inlineStr"/>
+      <c r="I55" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J55" s="68" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="67" t="n">
+        <v>36</v>
+      </c>
+      <c r="B56" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-21 (Mon)</t>
+        </is>
+      </c>
+      <c r="C56" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D56" s="68" t="inlineStr">
+        <is>
+          <t>Backlink Outreach</t>
+        </is>
+      </c>
+      <c r="E56" s="68" t="inlineStr">
+        <is>
+          <t>Send/follow up outreach: SAIL – Steel Authority of India (request project mention/testimonial link)</t>
+        </is>
+      </c>
+      <c r="F56" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G56" s="68" t="inlineStr">
+        <is>
+          <t>1 personalized email + LinkedIn touch; log response in Change Log</t>
+        </is>
+      </c>
+      <c r="H56" s="67" t="inlineStr"/>
+      <c r="I56" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J56" s="68" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="67" t="n">
+        <v>37</v>
+      </c>
+      <c r="B57" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-22 (Tue)</t>
+        </is>
+      </c>
+      <c r="C57" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D57" s="68" t="inlineStr">
+        <is>
+          <t>Technical SEO</t>
+        </is>
+      </c>
+      <c r="E57" s="68" t="inlineStr">
+        <is>
+          <t>Audit indexing status, 404s, canonical tags, sitemap and schema for a batch of 10 pages; fix any issues found</t>
+        </is>
+      </c>
+      <c r="F57" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G57" s="68" t="inlineStr">
+        <is>
+          <t>0 broken links/pages in the batch reviewed</t>
+        </is>
+      </c>
+      <c r="H57" s="67" t="inlineStr"/>
+      <c r="I57" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J57" s="68" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="67" t="n">
+        <v>38</v>
+      </c>
+      <c r="B58" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-23 (Wed)</t>
+        </is>
+      </c>
+      <c r="C58" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D58" s="68" t="inlineStr">
+        <is>
+          <t>On-Page SEO</t>
+        </is>
+      </c>
+      <c r="E58" s="68" t="inlineStr">
+        <is>
+          <t>Review keyword targeting, internal linking, title/meta length for a batch of pages in SEO Tracker; update as needed</t>
+        </is>
+      </c>
+      <c r="F58" s="67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G58" s="68" t="inlineStr">
+        <is>
+          <t>All titles ≤60 chars, meta ≤155 chars, ≥3 internal links per page</t>
+        </is>
+      </c>
+      <c r="H58" s="67" t="inlineStr"/>
+      <c r="I58" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J58" s="68" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="67" t="n">
+        <v>39</v>
+      </c>
+      <c r="B59" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-24 (Thu)</t>
+        </is>
+      </c>
+      <c r="C59" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D59" s="68" t="inlineStr">
+        <is>
+          <t>PR / Guest Posting</t>
+        </is>
+      </c>
+      <c r="E59" s="68" t="inlineStr">
+        <is>
+          <t>Pitch or draft one guest article / press story (AICCC, BridgePulse, or a technical SHM/fatigue piece repurposed for a trade publication)</t>
+        </is>
+      </c>
+      <c r="F59" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G59" s="68" t="inlineStr">
+        <is>
+          <t>1 pitch sent or 1 draft completed</t>
+        </is>
+      </c>
+      <c r="H59" s="67" t="inlineStr"/>
+      <c r="I59" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J59" s="68" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="67" t="n">
+        <v>40</v>
+      </c>
+      <c r="B60" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-25 (Fri)</t>
+        </is>
+      </c>
+      <c r="C60" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D60" s="68" t="inlineStr">
+        <is>
+          <t>Tracking &amp; Reporting</t>
+        </is>
+      </c>
+      <c r="E60" s="68" t="inlineStr">
+        <is>
+          <t>Update DR/backlink/referring-domain snapshot; check Google Search Console for indexing and query changes; log results in this sheet</t>
+        </is>
+      </c>
+      <c r="F60" s="67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G60" s="68" t="inlineStr">
+        <is>
+          <t>Weekly metrics logged; Status column updated for the week</t>
+        </is>
+      </c>
+      <c r="H60" s="67" t="inlineStr"/>
+      <c r="I60" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J60" s="68" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="67" t="n">
+        <v>41</v>
+      </c>
+      <c r="B61" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-26 (Sat)</t>
+        </is>
+      </c>
+      <c r="C61" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D61" s="68" t="inlineStr">
+        <is>
+          <t>Content Prep</t>
+        </is>
+      </c>
+      <c r="E61" s="68" t="inlineStr">
+        <is>
+          <t>Batch-draft or repurpose content for next week's guest post / PR pitch / internal linking pass</t>
+        </is>
+      </c>
+      <c r="F61" s="67" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G61" s="68" t="inlineStr">
+        <is>
+          <t>1 draft asset queued</t>
+        </is>
+      </c>
+      <c r="H61" s="67" t="inlineStr"/>
+      <c r="I61" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J61" s="68" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="67" t="n">
+        <v>42</v>
+      </c>
+      <c r="B62" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-27 (Sun)</t>
+        </is>
+      </c>
+      <c r="C62" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D62" s="68" t="inlineStr">
+        <is>
+          <t>Buffer</t>
+        </is>
+      </c>
+      <c r="E62" s="68" t="inlineStr">
+        <is>
+          <t>No scheduled outreach — buffer day / catch up on any slipped tasks</t>
+        </is>
+      </c>
+      <c r="F62" s="67" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G62" s="68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H62" s="67" t="inlineStr"/>
+      <c r="I62" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J62" s="68" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="67" t="n">
+        <v>43</v>
+      </c>
+      <c r="B63" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-28 (Mon)</t>
+        </is>
+      </c>
+      <c r="C63" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D63" s="68" t="inlineStr">
+        <is>
+          <t>Backlink Outreach</t>
+        </is>
+      </c>
+      <c r="E63" s="68" t="inlineStr">
+        <is>
+          <t>Send/follow up outreach: BWSSB Karnataka (request project mention/testimonial link)</t>
+        </is>
+      </c>
+      <c r="F63" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G63" s="68" t="inlineStr">
+        <is>
+          <t>1 personalized email + LinkedIn touch; log response in Change Log</t>
+        </is>
+      </c>
+      <c r="H63" s="67" t="inlineStr"/>
+      <c r="I63" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J63" s="68" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="67" t="n">
+        <v>44</v>
+      </c>
+      <c r="B64" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-29 (Tue)</t>
+        </is>
+      </c>
+      <c r="C64" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D64" s="68" t="inlineStr">
+        <is>
+          <t>Technical SEO</t>
+        </is>
+      </c>
+      <c r="E64" s="68" t="inlineStr">
+        <is>
+          <t>Audit indexing status, 404s, canonical tags, sitemap and schema for a batch of 10 pages; fix any issues found</t>
+        </is>
+      </c>
+      <c r="F64" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G64" s="68" t="inlineStr">
+        <is>
+          <t>0 broken links/pages in the batch reviewed</t>
+        </is>
+      </c>
+      <c r="H64" s="67" t="inlineStr"/>
+      <c r="I64" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J64" s="68" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="67" t="n">
+        <v>45</v>
+      </c>
+      <c r="B65" s="67" t="inlineStr">
+        <is>
+          <t>2026-09-30 (Wed)</t>
+        </is>
+      </c>
+      <c r="C65" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D65" s="68" t="inlineStr">
+        <is>
+          <t>On-Page SEO</t>
+        </is>
+      </c>
+      <c r="E65" s="68" t="inlineStr">
+        <is>
+          <t>Review keyword targeting, internal linking, title/meta length for a batch of pages in SEO Tracker; update as needed</t>
+        </is>
+      </c>
+      <c r="F65" s="67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G65" s="68" t="inlineStr">
+        <is>
+          <t>All titles ≤60 chars, meta ≤155 chars, ≥3 internal links per page</t>
+        </is>
+      </c>
+      <c r="H65" s="67" t="inlineStr"/>
+      <c r="I65" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J65" s="68" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="67" t="n">
+        <v>46</v>
+      </c>
+      <c r="B66" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-01 (Thu)</t>
+        </is>
+      </c>
+      <c r="C66" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D66" s="68" t="inlineStr">
+        <is>
+          <t>PR / Guest Posting</t>
+        </is>
+      </c>
+      <c r="E66" s="68" t="inlineStr">
+        <is>
+          <t>Pitch or draft one guest article / press story (AICCC, BridgePulse, or a technical SHM/fatigue piece repurposed for a trade publication)</t>
+        </is>
+      </c>
+      <c r="F66" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G66" s="68" t="inlineStr">
+        <is>
+          <t>1 pitch sent or 1 draft completed</t>
+        </is>
+      </c>
+      <c r="H66" s="67" t="inlineStr"/>
+      <c r="I66" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J66" s="68" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="67" t="n">
+        <v>47</v>
+      </c>
+      <c r="B67" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-02 (Fri)</t>
+        </is>
+      </c>
+      <c r="C67" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D67" s="68" t="inlineStr">
+        <is>
+          <t>Tracking &amp; Reporting</t>
+        </is>
+      </c>
+      <c r="E67" s="68" t="inlineStr">
+        <is>
+          <t>Update DR/backlink/referring-domain snapshot; check Google Search Console for indexing and query changes; log results in this sheet</t>
+        </is>
+      </c>
+      <c r="F67" s="67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G67" s="68" t="inlineStr">
+        <is>
+          <t>Weekly metrics logged; Status column updated for the week</t>
+        </is>
+      </c>
+      <c r="H67" s="67" t="inlineStr"/>
+      <c r="I67" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J67" s="68" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="67" t="n">
+        <v>48</v>
+      </c>
+      <c r="B68" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-03 (Sat)</t>
+        </is>
+      </c>
+      <c r="C68" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D68" s="68" t="inlineStr">
+        <is>
+          <t>Content Prep</t>
+        </is>
+      </c>
+      <c r="E68" s="68" t="inlineStr">
+        <is>
+          <t>Batch-draft or repurpose content for next week's guest post / PR pitch / internal linking pass</t>
+        </is>
+      </c>
+      <c r="F68" s="67" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G68" s="68" t="inlineStr">
+        <is>
+          <t>1 draft asset queued</t>
+        </is>
+      </c>
+      <c r="H68" s="67" t="inlineStr"/>
+      <c r="I68" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J68" s="68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="67" t="n">
+        <v>49</v>
+      </c>
+      <c r="B69" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-04 (Sun)</t>
+        </is>
+      </c>
+      <c r="C69" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D69" s="68" t="inlineStr">
+        <is>
+          <t>Buffer</t>
+        </is>
+      </c>
+      <c r="E69" s="68" t="inlineStr">
+        <is>
+          <t>No scheduled outreach — buffer day / catch up on any slipped tasks</t>
+        </is>
+      </c>
+      <c r="F69" s="67" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G69" s="68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="67" t="inlineStr"/>
+      <c r="I69" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J69" s="68" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="67" t="n">
+        <v>50</v>
+      </c>
+      <c r="B70" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-05 (Mon)</t>
+        </is>
+      </c>
+      <c r="C70" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D70" s="68" t="inlineStr">
+        <is>
+          <t>Backlink Outreach</t>
+        </is>
+      </c>
+      <c r="E70" s="68" t="inlineStr">
+        <is>
+          <t>Send/follow up outreach: APTIDCO (request project mention/testimonial link)</t>
+        </is>
+      </c>
+      <c r="F70" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G70" s="68" t="inlineStr">
+        <is>
+          <t>1 personalized email + LinkedIn touch; log response in Change Log</t>
+        </is>
+      </c>
+      <c r="H70" s="67" t="inlineStr"/>
+      <c r="I70" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J70" s="68" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="67" t="n">
+        <v>51</v>
+      </c>
+      <c r="B71" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-06 (Tue)</t>
+        </is>
+      </c>
+      <c r="C71" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D71" s="68" t="inlineStr">
+        <is>
+          <t>Technical SEO</t>
+        </is>
+      </c>
+      <c r="E71" s="68" t="inlineStr">
+        <is>
+          <t>Audit indexing status, 404s, canonical tags, sitemap and schema for a batch of 10 pages; fix any issues found</t>
+        </is>
+      </c>
+      <c r="F71" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G71" s="68" t="inlineStr">
+        <is>
+          <t>0 broken links/pages in the batch reviewed</t>
+        </is>
+      </c>
+      <c r="H71" s="67" t="inlineStr"/>
+      <c r="I71" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J71" s="68" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="67" t="n">
+        <v>52</v>
+      </c>
+      <c r="B72" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-07 (Wed)</t>
+        </is>
+      </c>
+      <c r="C72" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D72" s="68" t="inlineStr">
+        <is>
+          <t>On-Page SEO</t>
+        </is>
+      </c>
+      <c r="E72" s="68" t="inlineStr">
+        <is>
+          <t>Review keyword targeting, internal linking, title/meta length for a batch of pages in SEO Tracker; update as needed</t>
+        </is>
+      </c>
+      <c r="F72" s="67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G72" s="68" t="inlineStr">
+        <is>
+          <t>All titles ≤60 chars, meta ≤155 chars, ≥3 internal links per page</t>
+        </is>
+      </c>
+      <c r="H72" s="67" t="inlineStr"/>
+      <c r="I72" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J72" s="68" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="67" t="n">
+        <v>53</v>
+      </c>
+      <c r="B73" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-08 (Thu)</t>
+        </is>
+      </c>
+      <c r="C73" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D73" s="68" t="inlineStr">
+        <is>
+          <t>PR / Guest Posting</t>
+        </is>
+      </c>
+      <c r="E73" s="68" t="inlineStr">
+        <is>
+          <t>Pitch or draft one guest article / press story (AICCC, BridgePulse, or a technical SHM/fatigue piece repurposed for a trade publication)</t>
+        </is>
+      </c>
+      <c r="F73" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G73" s="68" t="inlineStr">
+        <is>
+          <t>1 pitch sent or 1 draft completed</t>
+        </is>
+      </c>
+      <c r="H73" s="67" t="inlineStr"/>
+      <c r="I73" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J73" s="68" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="67" t="n">
+        <v>54</v>
+      </c>
+      <c r="B74" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-09 (Fri)</t>
+        </is>
+      </c>
+      <c r="C74" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D74" s="68" t="inlineStr">
+        <is>
+          <t>Tracking &amp; Reporting</t>
+        </is>
+      </c>
+      <c r="E74" s="68" t="inlineStr">
+        <is>
+          <t>Update DR/backlink/referring-domain snapshot; check Google Search Console for indexing and query changes; log results in this sheet</t>
+        </is>
+      </c>
+      <c r="F74" s="67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G74" s="68" t="inlineStr">
+        <is>
+          <t>Weekly metrics logged; Status column updated for the week</t>
+        </is>
+      </c>
+      <c r="H74" s="67" t="inlineStr"/>
+      <c r="I74" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J74" s="68" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="67" t="n">
+        <v>55</v>
+      </c>
+      <c r="B75" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-10 (Sat)</t>
+        </is>
+      </c>
+      <c r="C75" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D75" s="68" t="inlineStr">
+        <is>
+          <t>Content Prep</t>
+        </is>
+      </c>
+      <c r="E75" s="68" t="inlineStr">
+        <is>
+          <t>Batch-draft or repurpose content for next week's guest post / PR pitch / internal linking pass</t>
+        </is>
+      </c>
+      <c r="F75" s="67" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G75" s="68" t="inlineStr">
+        <is>
+          <t>1 draft asset queued</t>
+        </is>
+      </c>
+      <c r="H75" s="67" t="inlineStr"/>
+      <c r="I75" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J75" s="68" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="67" t="n">
+        <v>56</v>
+      </c>
+      <c r="B76" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-11 (Sun)</t>
+        </is>
+      </c>
+      <c r="C76" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D76" s="68" t="inlineStr">
+        <is>
+          <t>Buffer</t>
+        </is>
+      </c>
+      <c r="E76" s="68" t="inlineStr">
+        <is>
+          <t>No scheduled outreach — buffer day / catch up on any slipped tasks</t>
+        </is>
+      </c>
+      <c r="F76" s="67" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G76" s="68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="67" t="inlineStr"/>
+      <c r="I76" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J76" s="68" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="67" t="n">
+        <v>57</v>
+      </c>
+      <c r="B77" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-12 (Mon)</t>
+        </is>
+      </c>
+      <c r="C77" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D77" s="68" t="inlineStr">
+        <is>
+          <t>Backlink Outreach</t>
+        </is>
+      </c>
+      <c r="E77" s="68" t="inlineStr">
+        <is>
+          <t>Send/follow up outreach: Indian Railways – Southern Railway (follow-up outreach for project mention)</t>
+        </is>
+      </c>
+      <c r="F77" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G77" s="68" t="inlineStr">
+        <is>
+          <t>1 personalized email + LinkedIn touch; log response in Change Log</t>
+        </is>
+      </c>
+      <c r="H77" s="67" t="inlineStr"/>
+      <c r="I77" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J77" s="68" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="67" t="n">
+        <v>58</v>
+      </c>
+      <c r="B78" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-13 (Tue)</t>
+        </is>
+      </c>
+      <c r="C78" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D78" s="68" t="inlineStr">
+        <is>
+          <t>Technical SEO</t>
+        </is>
+      </c>
+      <c r="E78" s="68" t="inlineStr">
+        <is>
+          <t>Audit indexing status, 404s, canonical tags, sitemap and schema for a batch of 10 pages; fix any issues found</t>
+        </is>
+      </c>
+      <c r="F78" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G78" s="68" t="inlineStr">
+        <is>
+          <t>0 broken links/pages in the batch reviewed</t>
+        </is>
+      </c>
+      <c r="H78" s="67" t="inlineStr"/>
+      <c r="I78" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J78" s="68" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="67" t="n">
+        <v>59</v>
+      </c>
+      <c r="B79" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-14 (Wed)</t>
+        </is>
+      </c>
+      <c r="C79" s="67" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D79" s="68" t="inlineStr">
+        <is>
+          <t>On-Page SEO</t>
+        </is>
+      </c>
+      <c r="E79" s="68" t="inlineStr">
+        <is>
+          <t>Review keyword targeting, internal linking, title/meta length for a batch of pages in SEO Tracker; update as needed</t>
+        </is>
+      </c>
+      <c r="F79" s="67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G79" s="68" t="inlineStr">
+        <is>
+          <t>All titles ≤60 chars, meta ≤155 chars, ≥3 internal links per page</t>
+        </is>
+      </c>
+      <c r="H79" s="67" t="inlineStr"/>
+      <c r="I79" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J79" s="68" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="70" t="n">
+        <v>60</v>
+      </c>
+      <c r="B80" s="70" t="inlineStr">
+        <is>
+          <t>2026-10-15 (Thu)</t>
+        </is>
+      </c>
+      <c r="C80" s="70" t="inlineStr">
+        <is>
+          <t>Month 2 — Scale Outreach</t>
+        </is>
+      </c>
+      <c r="D80" s="71" t="inlineStr">
+        <is>
+          <t>Milestone Review</t>
+        </is>
+      </c>
+      <c r="E80" s="71" t="inlineStr">
+        <is>
+          <t>Month 2 review: confirm new DR20+ referring domains, published guest post, and government/PSU outreach status. Reassess which channels are converting and double down on those for Month 3.</t>
+        </is>
+      </c>
+      <c r="F80" s="70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G80" s="71" t="inlineStr">
+        <is>
+          <t>Month checkpoint completed and documented</t>
+        </is>
+      </c>
+      <c r="H80" s="70" t="inlineStr"/>
+      <c r="I80" s="70" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J80" s="71" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="67" t="n">
+        <v>61</v>
+      </c>
+      <c r="B81" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-16 (Fri)</t>
+        </is>
+      </c>
+      <c r="C81" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D81" s="68" t="inlineStr">
+        <is>
+          <t>Tracking &amp; Reporting</t>
+        </is>
+      </c>
+      <c r="E81" s="68" t="inlineStr">
+        <is>
+          <t>Update DR/backlink/referring-domain snapshot; check Google Search Console for indexing and query changes; log results in this sheet</t>
+        </is>
+      </c>
+      <c r="F81" s="67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G81" s="68" t="inlineStr">
+        <is>
+          <t>Weekly metrics logged; Status column updated for the week</t>
+        </is>
+      </c>
+      <c r="H81" s="67" t="inlineStr"/>
+      <c r="I81" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J81" s="68" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="67" t="n">
+        <v>62</v>
+      </c>
+      <c r="B82" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-17 (Sat)</t>
+        </is>
+      </c>
+      <c r="C82" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D82" s="68" t="inlineStr">
+        <is>
+          <t>Content Prep</t>
+        </is>
+      </c>
+      <c r="E82" s="68" t="inlineStr">
+        <is>
+          <t>Batch-draft or repurpose content for next week's guest post / PR pitch / internal linking pass</t>
+        </is>
+      </c>
+      <c r="F82" s="67" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G82" s="68" t="inlineStr">
+        <is>
+          <t>1 draft asset queued</t>
+        </is>
+      </c>
+      <c r="H82" s="67" t="inlineStr"/>
+      <c r="I82" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J82" s="68" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="67" t="n">
+        <v>63</v>
+      </c>
+      <c r="B83" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-18 (Sun)</t>
+        </is>
+      </c>
+      <c r="C83" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D83" s="68" t="inlineStr">
+        <is>
+          <t>Buffer</t>
+        </is>
+      </c>
+      <c r="E83" s="68" t="inlineStr">
+        <is>
+          <t>No scheduled outreach — buffer day / catch up on any slipped tasks</t>
+        </is>
+      </c>
+      <c r="F83" s="67" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G83" s="68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H83" s="67" t="inlineStr"/>
+      <c r="I83" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J83" s="68" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="67" t="n">
+        <v>64</v>
+      </c>
+      <c r="B84" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-19 (Mon)</t>
+        </is>
+      </c>
+      <c r="C84" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D84" s="68" t="inlineStr">
+        <is>
+          <t>Backlink Outreach</t>
+        </is>
+      </c>
+      <c r="E84" s="68" t="inlineStr">
+        <is>
+          <t>Send/follow up outreach: HappyNest (existing client — request testimonial/case-study backlink)</t>
+        </is>
+      </c>
+      <c r="F84" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G84" s="68" t="inlineStr">
+        <is>
+          <t>1 personalized email + LinkedIn touch; log response in Change Log</t>
+        </is>
+      </c>
+      <c r="H84" s="67" t="inlineStr"/>
+      <c r="I84" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J84" s="68" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B85" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-20 (Tue)</t>
+        </is>
+      </c>
+      <c r="C85" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D85" s="68" t="inlineStr">
+        <is>
+          <t>Technical SEO</t>
+        </is>
+      </c>
+      <c r="E85" s="68" t="inlineStr">
+        <is>
+          <t>Audit indexing status, 404s, canonical tags, sitemap and schema for a batch of 10 pages; fix any issues found</t>
+        </is>
+      </c>
+      <c r="F85" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G85" s="68" t="inlineStr">
+        <is>
+          <t>0 broken links/pages in the batch reviewed</t>
+        </is>
+      </c>
+      <c r="H85" s="67" t="inlineStr"/>
+      <c r="I85" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J85" s="68" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B86" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-21 (Wed)</t>
+        </is>
+      </c>
+      <c r="C86" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D86" s="68" t="inlineStr">
+        <is>
+          <t>On-Page SEO</t>
+        </is>
+      </c>
+      <c r="E86" s="68" t="inlineStr">
+        <is>
+          <t>Review keyword targeting, internal linking, title/meta length for a batch of pages in SEO Tracker; update as needed</t>
+        </is>
+      </c>
+      <c r="F86" s="67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G86" s="68" t="inlineStr">
+        <is>
+          <t>All titles ≤60 chars, meta ≤155 chars, ≥3 internal links per page</t>
+        </is>
+      </c>
+      <c r="H86" s="67" t="inlineStr"/>
+      <c r="I86" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J86" s="68" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="67" t="n">
+        <v>67</v>
+      </c>
+      <c r="B87" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-22 (Thu)</t>
+        </is>
+      </c>
+      <c r="C87" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D87" s="68" t="inlineStr">
+        <is>
+          <t>PR / Guest Posting</t>
+        </is>
+      </c>
+      <c r="E87" s="68" t="inlineStr">
+        <is>
+          <t>Pitch or draft one guest article / press story (AICCC, BridgePulse, or a technical SHM/fatigue piece repurposed for a trade publication)</t>
+        </is>
+      </c>
+      <c r="F87" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G87" s="68" t="inlineStr">
+        <is>
+          <t>1 pitch sent or 1 draft completed</t>
+        </is>
+      </c>
+      <c r="H87" s="67" t="inlineStr"/>
+      <c r="I87" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J87" s="68" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="67" t="n">
+        <v>68</v>
+      </c>
+      <c r="B88" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-23 (Fri)</t>
+        </is>
+      </c>
+      <c r="C88" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D88" s="68" t="inlineStr">
+        <is>
+          <t>Tracking &amp; Reporting</t>
+        </is>
+      </c>
+      <c r="E88" s="68" t="inlineStr">
+        <is>
+          <t>Update DR/backlink/referring-domain snapshot; check Google Search Console for indexing and query changes; log results in this sheet</t>
+        </is>
+      </c>
+      <c r="F88" s="67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G88" s="68" t="inlineStr">
+        <is>
+          <t>Weekly metrics logged; Status column updated for the week</t>
+        </is>
+      </c>
+      <c r="H88" s="67" t="inlineStr"/>
+      <c r="I88" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J88" s="68" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="67" t="n">
+        <v>69</v>
+      </c>
+      <c r="B89" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-24 (Sat)</t>
+        </is>
+      </c>
+      <c r="C89" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D89" s="68" t="inlineStr">
+        <is>
+          <t>Content Prep</t>
+        </is>
+      </c>
+      <c r="E89" s="68" t="inlineStr">
+        <is>
+          <t>Batch-draft or repurpose content for next week's guest post / PR pitch / internal linking pass</t>
+        </is>
+      </c>
+      <c r="F89" s="67" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G89" s="68" t="inlineStr">
+        <is>
+          <t>1 draft asset queued</t>
+        </is>
+      </c>
+      <c r="H89" s="67" t="inlineStr"/>
+      <c r="I89" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J89" s="68" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="67" t="n">
+        <v>70</v>
+      </c>
+      <c r="B90" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-25 (Sun)</t>
+        </is>
+      </c>
+      <c r="C90" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D90" s="68" t="inlineStr">
+        <is>
+          <t>Buffer</t>
+        </is>
+      </c>
+      <c r="E90" s="68" t="inlineStr">
+        <is>
+          <t>No scheduled outreach — buffer day / catch up on any slipped tasks</t>
+        </is>
+      </c>
+      <c r="F90" s="67" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G90" s="68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H90" s="67" t="inlineStr"/>
+      <c r="I90" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J90" s="68" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="67" t="n">
+        <v>71</v>
+      </c>
+      <c r="B91" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-26 (Mon)</t>
+        </is>
+      </c>
+      <c r="C91" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D91" s="68" t="inlineStr">
+        <is>
+          <t>Backlink Outreach</t>
+        </is>
+      </c>
+      <c r="E91" s="68" t="inlineStr">
+        <is>
+          <t>Send/follow up outreach: Industry association membership push (CII / FICCI infrastructure-tech chapter)</t>
+        </is>
+      </c>
+      <c r="F91" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G91" s="68" t="inlineStr">
+        <is>
+          <t>1 personalized email + LinkedIn touch; log response in Change Log</t>
+        </is>
+      </c>
+      <c r="H91" s="67" t="inlineStr"/>
+      <c r="I91" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J91" s="68" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="67" t="n">
+        <v>72</v>
+      </c>
+      <c r="B92" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-27 (Tue)</t>
+        </is>
+      </c>
+      <c r="C92" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D92" s="68" t="inlineStr">
+        <is>
+          <t>Technical SEO</t>
+        </is>
+      </c>
+      <c r="E92" s="68" t="inlineStr">
+        <is>
+          <t>Audit indexing status, 404s, canonical tags, sitemap and schema for a batch of 10 pages; fix any issues found</t>
+        </is>
+      </c>
+      <c r="F92" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G92" s="68" t="inlineStr">
+        <is>
+          <t>0 broken links/pages in the batch reviewed</t>
+        </is>
+      </c>
+      <c r="H92" s="67" t="inlineStr"/>
+      <c r="I92" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J92" s="68" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="67" t="n">
+        <v>73</v>
+      </c>
+      <c r="B93" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-28 (Wed)</t>
+        </is>
+      </c>
+      <c r="C93" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D93" s="68" t="inlineStr">
+        <is>
+          <t>On-Page SEO</t>
+        </is>
+      </c>
+      <c r="E93" s="68" t="inlineStr">
+        <is>
+          <t>Review keyword targeting, internal linking, title/meta length for a batch of pages in SEO Tracker; update as needed</t>
+        </is>
+      </c>
+      <c r="F93" s="67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G93" s="68" t="inlineStr">
+        <is>
+          <t>All titles ≤60 chars, meta ≤155 chars, ≥3 internal links per page</t>
+        </is>
+      </c>
+      <c r="H93" s="67" t="inlineStr"/>
+      <c r="I93" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J93" s="68" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="67" t="n">
+        <v>74</v>
+      </c>
+      <c r="B94" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-29 (Thu)</t>
+        </is>
+      </c>
+      <c r="C94" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D94" s="68" t="inlineStr">
+        <is>
+          <t>PR / Guest Posting</t>
+        </is>
+      </c>
+      <c r="E94" s="68" t="inlineStr">
+        <is>
+          <t>Pitch or draft one guest article / press story (AICCC, BridgePulse, or a technical SHM/fatigue piece repurposed for a trade publication)</t>
+        </is>
+      </c>
+      <c r="F94" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G94" s="68" t="inlineStr">
+        <is>
+          <t>1 pitch sent or 1 draft completed</t>
+        </is>
+      </c>
+      <c r="H94" s="67" t="inlineStr"/>
+      <c r="I94" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J94" s="68" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="67" t="n">
+        <v>75</v>
+      </c>
+      <c r="B95" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-30 (Fri)</t>
+        </is>
+      </c>
+      <c r="C95" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D95" s="68" t="inlineStr">
+        <is>
+          <t>Tracking &amp; Reporting</t>
+        </is>
+      </c>
+      <c r="E95" s="68" t="inlineStr">
+        <is>
+          <t>Update DR/backlink/referring-domain snapshot; check Google Search Console for indexing and query changes; log results in this sheet</t>
+        </is>
+      </c>
+      <c r="F95" s="67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G95" s="68" t="inlineStr">
+        <is>
+          <t>Weekly metrics logged; Status column updated for the week</t>
+        </is>
+      </c>
+      <c r="H95" s="67" t="inlineStr"/>
+      <c r="I95" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J95" s="68" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="67" t="n">
+        <v>76</v>
+      </c>
+      <c r="B96" s="67" t="inlineStr">
+        <is>
+          <t>2026-10-31 (Sat)</t>
+        </is>
+      </c>
+      <c r="C96" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D96" s="68" t="inlineStr">
+        <is>
+          <t>Content Prep</t>
+        </is>
+      </c>
+      <c r="E96" s="68" t="inlineStr">
+        <is>
+          <t>Batch-draft or repurpose content for next week's guest post / PR pitch / internal linking pass</t>
+        </is>
+      </c>
+      <c r="F96" s="67" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G96" s="68" t="inlineStr">
+        <is>
+          <t>1 draft asset queued</t>
+        </is>
+      </c>
+      <c r="H96" s="67" t="inlineStr"/>
+      <c r="I96" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J96" s="68" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="67" t="n">
+        <v>77</v>
+      </c>
+      <c r="B97" s="67" t="inlineStr">
+        <is>
+          <t>2026-11-01 (Sun)</t>
+        </is>
+      </c>
+      <c r="C97" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D97" s="68" t="inlineStr">
+        <is>
+          <t>Buffer</t>
+        </is>
+      </c>
+      <c r="E97" s="68" t="inlineStr">
+        <is>
+          <t>No scheduled outreach — buffer day / catch up on any slipped tasks</t>
+        </is>
+      </c>
+      <c r="F97" s="67" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G97" s="68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H97" s="67" t="inlineStr"/>
+      <c r="I97" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J97" s="68" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="67" t="n">
+        <v>78</v>
+      </c>
+      <c r="B98" s="67" t="inlineStr">
+        <is>
+          <t>2026-11-02 (Mon)</t>
+        </is>
+      </c>
+      <c r="C98" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D98" s="68" t="inlineStr">
+        <is>
+          <t>Backlink Outreach</t>
+        </is>
+      </c>
+      <c r="E98" s="68" t="inlineStr">
+        <is>
+          <t>Send/follow up outreach: Second-round follow-up to all non-responders from Months 1–2</t>
+        </is>
+      </c>
+      <c r="F98" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G98" s="68" t="inlineStr">
+        <is>
+          <t>1 personalized email + LinkedIn touch; log response in Change Log</t>
+        </is>
+      </c>
+      <c r="H98" s="67" t="inlineStr"/>
+      <c r="I98" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J98" s="68" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="67" t="n">
+        <v>79</v>
+      </c>
+      <c r="B99" s="67" t="inlineStr">
+        <is>
+          <t>2026-11-03 (Tue)</t>
+        </is>
+      </c>
+      <c r="C99" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D99" s="68" t="inlineStr">
+        <is>
+          <t>Technical SEO</t>
+        </is>
+      </c>
+      <c r="E99" s="68" t="inlineStr">
+        <is>
+          <t>Audit indexing status, 404s, canonical tags, sitemap and schema for a batch of 10 pages; fix any issues found</t>
+        </is>
+      </c>
+      <c r="F99" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G99" s="68" t="inlineStr">
+        <is>
+          <t>0 broken links/pages in the batch reviewed</t>
+        </is>
+      </c>
+      <c r="H99" s="67" t="inlineStr"/>
+      <c r="I99" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J99" s="68" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="67" t="n">
+        <v>80</v>
+      </c>
+      <c r="B100" s="67" t="inlineStr">
+        <is>
+          <t>2026-11-04 (Wed)</t>
+        </is>
+      </c>
+      <c r="C100" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D100" s="68" t="inlineStr">
+        <is>
+          <t>On-Page SEO</t>
+        </is>
+      </c>
+      <c r="E100" s="68" t="inlineStr">
+        <is>
+          <t>Review keyword targeting, internal linking, title/meta length for a batch of pages in SEO Tracker; update as needed</t>
+        </is>
+      </c>
+      <c r="F100" s="67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G100" s="68" t="inlineStr">
+        <is>
+          <t>All titles ≤60 chars, meta ≤155 chars, ≥3 internal links per page</t>
+        </is>
+      </c>
+      <c r="H100" s="67" t="inlineStr"/>
+      <c r="I100" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J100" s="68" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="67" t="n">
+        <v>81</v>
+      </c>
+      <c r="B101" s="67" t="inlineStr">
+        <is>
+          <t>2026-11-05 (Thu)</t>
+        </is>
+      </c>
+      <c r="C101" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D101" s="68" t="inlineStr">
+        <is>
+          <t>PR / Guest Posting</t>
+        </is>
+      </c>
+      <c r="E101" s="68" t="inlineStr">
+        <is>
+          <t>Pitch or draft one guest article / press story (AICCC, BridgePulse, or a technical SHM/fatigue piece repurposed for a trade publication)</t>
+        </is>
+      </c>
+      <c r="F101" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G101" s="68" t="inlineStr">
+        <is>
+          <t>1 pitch sent or 1 draft completed</t>
+        </is>
+      </c>
+      <c r="H101" s="67" t="inlineStr"/>
+      <c r="I101" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J101" s="68" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="67" t="n">
+        <v>82</v>
+      </c>
+      <c r="B102" s="67" t="inlineStr">
+        <is>
+          <t>2026-11-06 (Fri)</t>
+        </is>
+      </c>
+      <c r="C102" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D102" s="68" t="inlineStr">
+        <is>
+          <t>Tracking &amp; Reporting</t>
+        </is>
+      </c>
+      <c r="E102" s="68" t="inlineStr">
+        <is>
+          <t>Update DR/backlink/referring-domain snapshot; check Google Search Console for indexing and query changes; log results in this sheet</t>
+        </is>
+      </c>
+      <c r="F102" s="67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G102" s="68" t="inlineStr">
+        <is>
+          <t>Weekly metrics logged; Status column updated for the week</t>
+        </is>
+      </c>
+      <c r="H102" s="67" t="inlineStr"/>
+      <c r="I102" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J102" s="68" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="67" t="n">
+        <v>83</v>
+      </c>
+      <c r="B103" s="67" t="inlineStr">
+        <is>
+          <t>2026-11-07 (Sat)</t>
+        </is>
+      </c>
+      <c r="C103" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D103" s="68" t="inlineStr">
+        <is>
+          <t>Content Prep</t>
+        </is>
+      </c>
+      <c r="E103" s="68" t="inlineStr">
+        <is>
+          <t>Batch-draft or repurpose content for next week's guest post / PR pitch / internal linking pass</t>
+        </is>
+      </c>
+      <c r="F103" s="67" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G103" s="68" t="inlineStr">
+        <is>
+          <t>1 draft asset queued</t>
+        </is>
+      </c>
+      <c r="H103" s="67" t="inlineStr"/>
+      <c r="I103" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J103" s="68" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="67" t="n">
+        <v>84</v>
+      </c>
+      <c r="B104" s="67" t="inlineStr">
+        <is>
+          <t>2026-11-08 (Sun)</t>
+        </is>
+      </c>
+      <c r="C104" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D104" s="68" t="inlineStr">
+        <is>
+          <t>Buffer</t>
+        </is>
+      </c>
+      <c r="E104" s="68" t="inlineStr">
+        <is>
+          <t>No scheduled outreach — buffer day / catch up on any slipped tasks</t>
+        </is>
+      </c>
+      <c r="F104" s="67" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G104" s="68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H104" s="67" t="inlineStr"/>
+      <c r="I104" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J104" s="68" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="67" t="n">
+        <v>85</v>
+      </c>
+      <c r="B105" s="67" t="inlineStr">
+        <is>
+          <t>2026-11-09 (Mon)</t>
+        </is>
+      </c>
+      <c r="C105" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D105" s="68" t="inlineStr">
+        <is>
+          <t>Backlink Outreach</t>
+        </is>
+      </c>
+      <c r="E105" s="68" t="inlineStr">
+        <is>
+          <t>Send/follow up outreach: New partner prospecting — identify 3 more DR30+ relevant sites to pitch</t>
+        </is>
+      </c>
+      <c r="F105" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G105" s="68" t="inlineStr">
+        <is>
+          <t>1 personalized email + LinkedIn touch; log response in Change Log</t>
+        </is>
+      </c>
+      <c r="H105" s="67" t="inlineStr"/>
+      <c r="I105" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J105" s="68" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="67" t="n">
+        <v>86</v>
+      </c>
+      <c r="B106" s="67" t="inlineStr">
+        <is>
+          <t>2026-11-10 (Tue)</t>
+        </is>
+      </c>
+      <c r="C106" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D106" s="68" t="inlineStr">
+        <is>
+          <t>Technical SEO</t>
+        </is>
+      </c>
+      <c r="E106" s="68" t="inlineStr">
+        <is>
+          <t>Audit indexing status, 404s, canonical tags, sitemap and schema for a batch of 10 pages; fix any issues found</t>
+        </is>
+      </c>
+      <c r="F106" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G106" s="68" t="inlineStr">
+        <is>
+          <t>0 broken links/pages in the batch reviewed</t>
+        </is>
+      </c>
+      <c r="H106" s="67" t="inlineStr"/>
+      <c r="I106" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J106" s="68" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="67" t="n">
+        <v>87</v>
+      </c>
+      <c r="B107" s="67" t="inlineStr">
+        <is>
+          <t>2026-11-11 (Wed)</t>
+        </is>
+      </c>
+      <c r="C107" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D107" s="68" t="inlineStr">
+        <is>
+          <t>On-Page SEO</t>
+        </is>
+      </c>
+      <c r="E107" s="68" t="inlineStr">
+        <is>
+          <t>Review keyword targeting, internal linking, title/meta length for a batch of pages in SEO Tracker; update as needed</t>
+        </is>
+      </c>
+      <c r="F107" s="67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G107" s="68" t="inlineStr">
+        <is>
+          <t>All titles ≤60 chars, meta ≤155 chars, ≥3 internal links per page</t>
+        </is>
+      </c>
+      <c r="H107" s="67" t="inlineStr"/>
+      <c r="I107" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J107" s="68" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="67" t="n">
+        <v>88</v>
+      </c>
+      <c r="B108" s="67" t="inlineStr">
+        <is>
+          <t>2026-11-12 (Thu)</t>
+        </is>
+      </c>
+      <c r="C108" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D108" s="68" t="inlineStr">
+        <is>
+          <t>PR / Guest Posting</t>
+        </is>
+      </c>
+      <c r="E108" s="68" t="inlineStr">
+        <is>
+          <t>Pitch or draft one guest article / press story (AICCC, BridgePulse, or a technical SHM/fatigue piece repurposed for a trade publication)</t>
+        </is>
+      </c>
+      <c r="F108" s="69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G108" s="68" t="inlineStr">
+        <is>
+          <t>1 pitch sent or 1 draft completed</t>
+        </is>
+      </c>
+      <c r="H108" s="67" t="inlineStr"/>
+      <c r="I108" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J108" s="68" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="67" t="n">
+        <v>89</v>
+      </c>
+      <c r="B109" s="67" t="inlineStr">
+        <is>
+          <t>2026-11-13 (Fri)</t>
+        </is>
+      </c>
+      <c r="C109" s="67" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D109" s="68" t="inlineStr">
+        <is>
+          <t>Tracking &amp; Reporting</t>
+        </is>
+      </c>
+      <c r="E109" s="68" t="inlineStr">
+        <is>
+          <t>Update DR/backlink/referring-domain snapshot; check Google Search Console for indexing and query changes; log results in this sheet</t>
+        </is>
+      </c>
+      <c r="F109" s="67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G109" s="68" t="inlineStr">
+        <is>
+          <t>Weekly metrics logged; Status column updated for the week</t>
+        </is>
+      </c>
+      <c r="H109" s="67" t="inlineStr"/>
+      <c r="I109" s="67" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J109" s="68" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="70" t="n">
+        <v>90</v>
+      </c>
+      <c r="B110" s="70" t="inlineStr">
+        <is>
+          <t>2026-11-14 (Sat)</t>
+        </is>
+      </c>
+      <c r="C110" s="70" t="inlineStr">
+        <is>
+          <t>Month 3 — Consolidate &amp; Review</t>
+        </is>
+      </c>
+      <c r="D110" s="71" t="inlineStr">
+        <is>
+          <t>Milestone Review</t>
+        </is>
+      </c>
+      <c r="E110" s="71" t="inlineStr">
+        <is>
+          <t>Quarter review: compare DR/UR/backlinks/organic keywords against Day-1 baseline, document what worked, and draft the next 90-day plan based on results.</t>
+        </is>
+      </c>
+      <c r="F110" s="70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G110" s="71" t="inlineStr">
+        <is>
+          <t>Full metrics comparison vs. baseline logged; next-quarter plan drafted</t>
+        </is>
+      </c>
+      <c r="H110" s="70" t="inlineStr"/>
+      <c r="I110" s="70" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J110" s="71" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B10:E10"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="I21:I110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not Started,In Progress,Done,Blocked"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -16997,7 +21679,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -17128,7 +21810,7 @@
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>HTTP status 404 on automated check.</t>
+          <t>HTTP status 404 on automated check. | Investigated 2026-08-15: file does not exist in the repo under any name in that directory — needs the real asset supplied, not a code fix.</t>
         </is>
       </c>
     </row>
@@ -17943,7 +22625,11 @@
           <t>/blogs/what-is-a-strain-gauge-types-working-principle.html</t>
         </is>
       </c>
-      <c r="E28" s="14" t="n"/>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
       <c r="F28" s="15" t="inlineStr">
         <is>
           <t>—</t>
@@ -17979,7 +22665,11 @@
           <t>/blogs/what-is-an-inclinometer-digital-tiltmeter-guide.html</t>
         </is>
       </c>
-      <c r="E29" s="14" t="n"/>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
       <c r="F29" s="15" t="inlineStr">
         <is>
           <t>—</t>
@@ -18015,7 +22705,11 @@
           <t>/blogs/what-is-an-accelerometer-sensor-guide.html</t>
         </is>
       </c>
-      <c r="E30" s="14" t="n"/>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
       <c r="F30" s="15" t="inlineStr">
         <is>
           <t>—</t>
@@ -18051,7 +22745,11 @@
           <t>/blogs/what-is-an-accelerometer-sensor-guide.html</t>
         </is>
       </c>
-      <c r="E31" s="14" t="n"/>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
       <c r="F31" s="15" t="inlineStr">
         <is>
           <t>—</t>
@@ -18123,7 +22821,11 @@
           <t>/blogs/what-is-a-data-logger-types-guide.html</t>
         </is>
       </c>
-      <c r="E33" s="14" t="n"/>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
       <c r="F33" s="15" t="inlineStr">
         <is>
           <t>—</t>
@@ -18483,7 +23185,11 @@
           <t>/products/lcc.html</t>
         </is>
       </c>
-      <c r="E43" s="14" t="n"/>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
       <c r="F43" s="15" t="inlineStr">
         <is>
           <t>—</t>
@@ -18555,7 +23261,11 @@
           <t>/products/lixelstudio.html</t>
         </is>
       </c>
-      <c r="E45" s="14" t="n"/>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
       <c r="F45" s="15" t="inlineStr">
         <is>
           <t>—</t>
@@ -18613,13 +23323,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.005" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
@@ -18710,6 +23420,18 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SEO Growth Plan (90-Day)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Day-by-day 90-day plan to raise Domain Rating and fix technical SEO, built from the 2026-08-15 Ahrefs review. Update the Status column weekly; review Milestone rows on Day 30/60/90.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
